--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484623_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484623_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5292</v>
+        <v>7.477</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4873</v>
+        <v>5.559</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0419</v>
+        <v>1.918</v>
       </c>
       <c r="G2" t="n">
         <v>1.8383</v>
@@ -610,13 +610,13 @@
         <v>2.7489</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.9398</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8627</v>
+        <v>0.2089</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8548</v>
+        <v>0.7309</v>
       </c>
       <c r="V2" t="n">
         <v>2.8663</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3015</v>
+        <v>5.8099</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8185</v>
+        <v>4.3517</v>
       </c>
       <c r="F3" t="n">
-        <v>1.483</v>
+        <v>1.4582</v>
       </c>
       <c r="G3" t="n">
         <v>1.6424</v>
@@ -688,13 +688,13 @@
         <v>2.1991</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8161</v>
+        <v>1.3245</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0423</v>
+        <v>0.5754</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7738</v>
+        <v>0.749</v>
       </c>
       <c r="V3" t="n">
         <v>0.6439</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5831</v>
+        <v>3.6544</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1031</v>
+        <v>0.1993</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4799</v>
+        <v>3.4551</v>
       </c>
       <c r="G4" t="n">
         <v>2.7013</v>
@@ -766,13 +766,13 @@
         <v>1.8326</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5702</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2187</v>
+        <v>0.3149</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3515</v>
+        <v>0.3267</v>
       </c>
       <c r="V4" t="n">
         <v>0.3115</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2663</v>
+        <v>2.9699</v>
       </c>
       <c r="E5" t="n">
-        <v>2.8658</v>
+        <v>2.4951</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4005</v>
+        <v>0.4748</v>
       </c>
       <c r="G5" t="n">
         <v>-1.118</v>
@@ -844,13 +844,13 @@
         <v>2.3823</v>
       </c>
       <c r="S5" t="n">
-        <v>1.68</v>
+        <v>1.3837</v>
       </c>
       <c r="T5" t="n">
-        <v>1.1154</v>
+        <v>0.7447</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5646</v>
+        <v>0.6389</v>
       </c>
       <c r="V5" t="n">
         <v>0.3219</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IGBINS DAVID</t>
+          <t>P. MORTE MONTANES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2413</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.8246</v>
+        <v>1.3759</v>
       </c>
       <c r="F6" t="n">
-        <v>2.066</v>
+        <v>-0.4147</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.156</v>
+        <v>0.2392</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0312</v>
+        <v>1.6975</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8752</v>
+        <v>-1.4583</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1451</v>
+        <v>1.0928</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.796</v>
+        <v>2.1983</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6509</v>
+        <v>-1.1055</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0109</v>
+        <v>-0.8535</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2351</v>
+        <v>-0.5008</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2243</v>
+        <v>-0.3528</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.5498</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.8326</v>
+      </c>
+      <c r="R6" t="n">
         <v>1.2828</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-0.9163</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.1991</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.4365</v>
+        <v>0.6278</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2368</v>
+        <v>0.2048</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1997</v>
+        <v>0.4231</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3219</v>
+        <v>0.6439</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.9109</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3219</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="7">
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SABATE PRATS</t>
+          <t>J. LE BERRE CASTILLO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6704</v>
+        <v>0.7664</v>
       </c>
       <c r="E8" t="n">
-        <v>0.678</v>
+        <v>-1.8288</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0076</v>
+        <v>2.5952</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0207</v>
+        <v>3.2972</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4503</v>
+        <v>3.1082</v>
       </c>
       <c r="I8" t="n">
-        <v>1.4297</v>
+        <v>0.189</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5378</v>
+        <v>3.212</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2043</v>
+        <v>3.0869</v>
       </c>
       <c r="L8" t="n">
-        <v>1.3336</v>
+        <v>0.125</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5585</v>
+        <v>0.0852</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.6546</v>
+        <v>0.0213</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0961</v>
+        <v>0.064</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3665</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.8326</v>
+        <v>-4.5814</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4661</v>
+        <v>2.5656</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4137</v>
+        <v>0.129</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3288</v>
+        <v>-0.1478</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0849</v>
+        <v>0.2767</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6439</v>
+        <v>-0.6439</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6439</v>
+        <v>-0.3115</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3324</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. CEJUDO GALÁN</t>
+          <t>A. IGBINS DAVID</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6251</v>
+        <v>0.6585</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6251</v>
+        <v>-1.2092</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.8678</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6251</v>
+        <v>-0.156</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-1.0312</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6251</v>
+        <v>0.8752</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6251</v>
+        <v>-0.1451</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.796</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6251</v>
+        <v>0.6509</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>-0.0109</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.2351</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.2243</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.2828</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.1991</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.1463</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.1478</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.0015</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MORTE MONTANES</t>
+          <t>A. CEJUDO GALÁN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6118</v>
+        <v>0.6251</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2246</v>
+        <v>0.6251</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6128</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2392</v>
+        <v>0.6251</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6975</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.4583</v>
+        <v>0.6251</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0928</v>
+        <v>0.6251</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1983</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1055</v>
+        <v>0.6251</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8535</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5008</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3528</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8326</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2828</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2784</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0536</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2249</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6439</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9109</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LE BERRE CASTILLO</t>
+          <t>J. SABATE PRATS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5249</v>
+        <v>0.5772</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2685</v>
+        <v>0.4857</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7934</v>
+        <v>0.0915</v>
       </c>
       <c r="G11" t="n">
-        <v>3.2972</v>
+        <v>-0.0207</v>
       </c>
       <c r="H11" t="n">
-        <v>3.1082</v>
+        <v>-1.4503</v>
       </c>
       <c r="I11" t="n">
-        <v>0.189</v>
+        <v>1.4297</v>
       </c>
       <c r="J11" t="n">
-        <v>3.212</v>
+        <v>1.5378</v>
       </c>
       <c r="K11" t="n">
-        <v>3.0869</v>
+        <v>0.2043</v>
       </c>
       <c r="L11" t="n">
-        <v>0.125</v>
+        <v>1.3336</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0852</v>
+        <v>-1.5585</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0213</v>
+        <v>-1.6546</v>
       </c>
       <c r="O11" t="n">
-        <v>0.064</v>
+        <v>0.0961</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0158</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.5814</v>
+        <v>-1.8326</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5656</v>
+        <v>1.4661</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1125</v>
+        <v>0.3205</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5875</v>
+        <v>0.1365</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4749</v>
+        <v>0.184</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.6439</v>
+        <v>0.6439</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.3115</v>
+        <v>0.6439</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.3324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.8578</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.641</v>
       </c>
       <c r="F12" t="n">
         <v>-0.2167</v>
@@ -1390,10 +1390,10 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0551</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0551</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.2906</v>
+        <v>-1.2163</v>
       </c>
       <c r="E13" t="n">
         <v>-1.6076</v>
       </c>
       <c r="F13" t="n">
-        <v>0.317</v>
+        <v>0.3914</v>
       </c>
       <c r="G13" t="n">
         <v>-1.065</v>
@@ -1468,13 +1468,13 @@
         <v>0.5498</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1707</v>
+        <v>-0.0963</v>
       </c>
       <c r="T13" t="n">
         <v>-0.092</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0043</v>
       </c>
       <c r="V13" t="n">
         <v>0.3115</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.5736</v>
+        <v>-1.3506</v>
       </c>
       <c r="E14" t="n">
         <v>-1.4068</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1668</v>
+        <v>0.0562</v>
       </c>
       <c r="G14" t="n">
         <v>-0.18</v>
@@ -1546,13 +1546,13 @@
         <v>1.4661</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6764</v>
+        <v>-0.4534</v>
       </c>
       <c r="T14" t="n">
         <v>-0.3122</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3642</v>
+        <v>-0.1412</v>
       </c>
       <c r="V14" t="n">
         <v>-1.267</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.1833</v>
+        <v>-2.1312</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.9477</v>
+        <v>-1.7965</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2356</v>
+        <v>-0.3347</v>
       </c>
       <c r="G15" t="n">
         <v>-1.1648</v>
@@ -1624,13 +1624,13 @@
         <v>0.5498</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0472</v>
+        <v>0.0049</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2753</v>
+        <v>-0.1241</v>
       </c>
       <c r="U15" t="n">
-        <v>0.228</v>
+        <v>0.129</v>
       </c>
       <c r="V15" t="n">
         <v>0.3115</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>18.3435</v>
+        <v>18.8939</v>
       </c>
       <c r="E16" t="n">
-        <v>7.001300000000003</v>
+        <v>7.552099999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>11.3422</v>
+        <v>11.3421</v>
       </c>
       <c r="G16" t="n">
         <v>6.731400000000002</v>
@@ -1678,7 +1678,7 @@
         <v>13.1372</v>
       </c>
       <c r="K16" t="n">
-        <v>9.448700000000001</v>
+        <v>9.448699999999999</v>
       </c>
       <c r="L16" t="n">
         <v>3.688599999999999</v>
@@ -1702,13 +1702,13 @@
         <v>19.2422</v>
       </c>
       <c r="S16" t="n">
-        <v>4.125099999999999</v>
+        <v>4.6758</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8107999999999999</v>
+        <v>1.3613</v>
       </c>
       <c r="U16" t="n">
-        <v>3.3142</v>
+        <v>3.3143</v>
       </c>
       <c r="V16" t="n">
         <v>3.821599999999999</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VERGARA APARICIO</t>
+          <t>P. PAREJA ANDRES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8673</v>
+        <v>2.4398</v>
       </c>
       <c r="E17" t="n">
-        <v>0.832</v>
+        <v>1.3509</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0353</v>
+        <v>1.0888</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3726</v>
+        <v>2.3291</v>
       </c>
       <c r="H17" t="n">
-        <v>0.054</v>
+        <v>-0.4981</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4266</v>
+        <v>2.8272</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3117</v>
+        <v>3.9292</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1609</v>
+        <v>0.6529</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1508</v>
+        <v>3.2764</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6843</v>
+        <v>-1.6002</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1069</v>
+        <v>-1.151</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5774</v>
+        <v>-0.4492</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3665</v>
+        <v>0.1833</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.733</v>
+        <v>-2.5656</v>
       </c>
       <c r="R17" t="n">
-        <v>1.0995</v>
+        <v>2.7489</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5722</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2429</v>
+        <v>-0.667</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3294</v>
+        <v>-0.0391</v>
       </c>
       <c r="V17" t="n">
-        <v>0.3011</v>
+        <v>0.6335</v>
       </c>
       <c r="W17" t="n">
-        <v>0.0104</v>
+        <v>0.6543</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2907</v>
+        <v>-0.0208</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. PAREJA ANDRES</t>
+          <t>T. ROIG ARIÑO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7506</v>
+        <v>1.2753</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0625</v>
+        <v>1.2753</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6881</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>2.3291</v>
+        <v>1.2753</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4981</v>
+        <v>0.6502</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8272</v>
+        <v>0.6251</v>
       </c>
       <c r="J18" t="n">
-        <v>3.9292</v>
+        <v>1.2753</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6529</v>
+        <v>0.6502</v>
       </c>
       <c r="L18" t="n">
-        <v>3.2764</v>
+        <v>0.6251</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6002</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.151</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4492</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.5656</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7489</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3952</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9555</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4398</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6335</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6543</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.0208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. ROIG ARIÑO</t>
+          <t>J. SÁEZ GONZÁLEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,28 +1891,28 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2753</v>
+        <v>0.9502</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2753</v>
+        <v>0.9502</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2753</v>
+        <v>0.9502</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="I19" t="n">
         <v>0.6251</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2753</v>
+        <v>0.9502</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6502</v>
+        <v>0.3251</v>
       </c>
       <c r="L19" t="n">
         <v>0.6251</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SÁEZ GONZÁLEZ</t>
+          <t>J. VERGARA APARICIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9502</v>
+        <v>0.5239</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9502</v>
+        <v>-0.3219</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.8458</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9502</v>
+        <v>-0.3726</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3251</v>
+        <v>0.054</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6251</v>
+        <v>-0.4266</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9502</v>
+        <v>0.3117</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3251</v>
+        <v>0.1609</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6251</v>
+        <v>0.1508</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>-0.6843</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.1069</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.5774</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.733</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.0995</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.2289</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.1399</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.3011</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.2907</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0646</v>
+        <v>0.187</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2427</v>
+        <v>0.435</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.178</v>
+        <v>-0.248</v>
       </c>
       <c r="G21" t="n">
         <v>0.364</v>
@@ -2092,13 +2092,13 @@
         <v>2.5656</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3885</v>
+        <v>-0.2662</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8258</v>
+        <v>-0.6335</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4372</v>
+        <v>0.3673</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6439</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4735</v>
+        <v>-1.0043</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.7634</v>
+        <v>-2.5711</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2899</v>
+        <v>1.5667</v>
       </c>
       <c r="G22" t="n">
         <v>-0.3629</v>
@@ -2170,13 +2170,13 @@
         <v>0.5498</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3775</v>
+        <v>0.0916</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1573</v>
+        <v>0.1195</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. DIAGO ROS</t>
+          <t>J. SAEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1843</v>
+        <v>-2.3453</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6571</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.5272</v>
+        <v>-2.9375</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6893</v>
+        <v>-0.7251</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1121</v>
+        <v>-0.677</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8014</v>
+        <v>-0.048</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2634</v>
+        <v>1.7329</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3777</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.641</v>
+        <v>0.7857</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4259</v>
+        <v>-2.4579</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2656</v>
+        <v>-1.6241</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.1603</v>
+        <v>-0.8338</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.3665</v>
+        <v>0.3665</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9163</v>
+        <v>-1.6493</v>
       </c>
       <c r="R24" t="n">
-        <v>0.5498</v>
+        <v>2.0158</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1385</v>
+        <v>-0.7198</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2006</v>
+        <v>-0.4468</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0621</v>
+        <v>-0.273</v>
       </c>
       <c r="V24" t="n">
         <v>-1.267</v>
       </c>
       <c r="W24" t="n">
-        <v>0.3219</v>
+        <v>0.9554</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.5889</v>
+        <v>-2.2224</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>J. SAEZ GONZALEZ</t>
+          <t>A. DIAGO ROS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.0593</v>
+        <v>-2.4698</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3037</v>
+        <v>-1.0417</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.363</v>
+        <v>-1.4281</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.7251</v>
+        <v>-0.6893</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.677</v>
+        <v>0.1121</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.048</v>
+        <v>-0.8014</v>
       </c>
       <c r="J25" t="n">
-        <v>1.7329</v>
+        <v>-0.2634</v>
       </c>
       <c r="K25" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.3777</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7857</v>
+        <v>-0.641</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4579</v>
+        <v>-0.4259</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6241</v>
+        <v>-0.2656</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.8338</v>
+        <v>-0.1603</v>
       </c>
       <c r="P25" t="n">
-        <v>0.3665</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.6493</v>
+        <v>-0.9163</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0158</v>
+        <v>0.5498</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.4338</v>
+        <v>-0.1471</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7353</v>
+        <v>-0.184</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6985</v>
+        <v>0.0369</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
       </c>
       <c r="W25" t="n">
-        <v>0.9554</v>
+        <v>0.3219</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.2224</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="26">
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.2368</v>
+        <v>-2.8668</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3134</v>
+        <v>-0.1211</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9234</v>
+        <v>-2.7456</v>
       </c>
       <c r="G26" t="n">
         <v>0.2355</v>
@@ -2482,13 +2482,13 @@
         <v>0.733</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4436</v>
+        <v>-0.0735</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.2202</v>
+        <v>-0.0279</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.2234</v>
+        <v>-0.0456</v>
       </c>
       <c r="V26" t="n">
         <v>-2.8455</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-3.455</v>
+        <v>-3.2277</v>
       </c>
       <c r="E27" t="n">
         <v>-0.4545</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.0005</v>
+        <v>-2.7732</v>
       </c>
       <c r="G27" t="n">
         <v>-2.0339</v>
@@ -2560,13 +2560,13 @@
         <v>0.3665</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.5207000000000001</v>
+        <v>-0.2934</v>
       </c>
       <c r="T27" t="n">
         <v>-0.3303</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.1903</v>
+        <v>0.0369</v>
       </c>
       <c r="V27" t="n">
         <v>-1.267</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.9755</v>
+        <v>-3.5588</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.2455</v>
+        <v>-2.957</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.73</v>
+        <v>-0.6018</v>
       </c>
       <c r="G28" t="n">
         <v>-1.9884</v>
@@ -2638,13 +2638,13 @@
         <v>1.2828</v>
       </c>
       <c r="S28" t="n">
-        <v>-0.5498</v>
+        <v>-0.1331</v>
       </c>
       <c r="T28" t="n">
-        <v>-0.4404</v>
+        <v>-0.152</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1094</v>
+        <v>0.0188</v>
       </c>
       <c r="V28" t="n">
         <v>0.945</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-5.3328</v>
+        <v>-5.4305</v>
       </c>
       <c r="E29" t="n">
-        <v>-6.2561</v>
+        <v>-6.1599</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9233</v>
+        <v>0.7294</v>
       </c>
       <c r="G29" t="n">
         <v>-6.038</v>
@@ -2716,13 +2716,13 @@
         <v>1.8326</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.122</v>
+        <v>-0.2196</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.5151</v>
+        <v>-0.4189</v>
       </c>
       <c r="U29" t="n">
-        <v>0.3931</v>
+        <v>0.1993</v>
       </c>
       <c r="V29" t="n">
         <v>0.6439</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-18.3437</v>
+        <v>-17.0615</v>
       </c>
       <c r="E30" t="n">
         <v>-11.3422</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.001399999999999</v>
+        <v>-5.719399999999999</v>
       </c>
       <c r="G30" t="n">
         <v>-6.7317</v>
@@ -2767,7 +2767,7 @@
         <v>-1.6034</v>
       </c>
       <c r="J30" t="n">
-        <v>6.405600000000002</v>
+        <v>6.405599999999998</v>
       </c>
       <c r="K30" t="n">
         <v>4.320500000000002</v>
@@ -2779,7 +2779,7 @@
         <v>-13.1374</v>
       </c>
       <c r="N30" t="n">
-        <v>-9.448700000000002</v>
+        <v>-9.448700000000001</v>
       </c>
       <c r="O30" t="n">
         <v>-3.6886</v>
@@ -2794,19 +2794,19 @@
         <v>15.5769</v>
       </c>
       <c r="S30" t="n">
-        <v>-4.1252</v>
+        <v>-2.8431</v>
       </c>
       <c r="T30" t="n">
         <v>-3.3144</v>
       </c>
       <c r="U30" t="n">
-        <v>-0.8109</v>
+        <v>0.4711</v>
       </c>
       <c r="V30" t="n">
         <v>-3.8219</v>
       </c>
       <c r="W30" t="n">
-        <v>4.808400000000001</v>
+        <v>4.8084</v>
       </c>
       <c r="X30" t="n">
         <v>-8.629999999999999</v>
